--- a/outputs/裂隙BOSS及召唤物技能伤害表.xlsx
+++ b/outputs/裂隙BOSS及召唤物技能伤害表.xlsx
@@ -101,7 +101,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 12,852-16,571；T2 17,993-23,199；T3 25,704-33,141（基础区间×武器调谐倍率1.2×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 12,853-16,572；T2 17,995-23,201；T3 25,707-33,144（基础区间×武器调谐倍率1.2×Boss模板×Tier）</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,916-16,418；T2 16,682-22,986；T3 23,832-32,837（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约50；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,189-13,429；T2 12,864-18,801；T3 18,377-26,858（基础区间×武器调谐倍率1.35×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约351-387；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,683-14,249；T2 13,557-19,949；T3 19,366-28,498（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约143-193；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 10,047-14,703；T2 14,066-20,584；T3 20,094-29,406（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约394-506；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 1,939-2,858；T2 2,715-4,001；T3 3,878-5,716（基础区间×武器调谐倍率1.25×damageCoefficient×0.7×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约36-48；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,227-3,063；T2 3,118-4,288；T3 4,454-6,126（基础区间×武器调谐倍率1.15×damageCoefficient×0.7×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约20；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,788-3,841；T2 3,903-5,378；T3 5,576-7,683（基础区间×武器调谐倍率1.45×damageCoefficient×0.7×Tier）</t>
+          <t xml:space="preserve">效果1：T1 1,050; T2 1,470; T3 2,100（召唤物伤害系数×0.7）（每跳）</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,843-16,346；T2 16,581-22,884；T3 23,687-32,692（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果2：T1 1,500; T2 2,100; T3 3,000（每跳）</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,905-16,398；T2 16,666-22,957；T3 23,809-32,796（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：T1 1,500; T2 2,100; T3 3,000（每跳）</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,919-16,412；T2 16,687-22,977；T3 23,838-32,825（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果2：DBC基础约10；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,488-13,051；T2 13,283-18,272；T3 18,975-26,102（基础区间×武器调谐倍率1.15×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果2：DBC基础约40；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,442-13,005；T2 13,218-18,207；T3 18,883-26,010（基础区间×武器调谐倍率1.15×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,443-13,006；T2 13,220-18,209；T3 18,886-26,013（基础区间×武器调谐倍率1.15×Boss模板×Tier）</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,102-3,078；T2 2,942-4,309；T3 4,203-6,155（基础区间×武器调谐倍率1.35×damageCoefficient×0.65×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约215-289；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,416-3,473；T2 3,382-4,863；T3 4,831-6,947（基础区间×武器调谐倍率1.45×damageCoefficient×0.65×Tier）；效果2：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,055-3,033；T2 2,877-4,246；T3 4,109-6,066（基础区间×武器调谐倍率1.45×damageCoefficient×0.65×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约383-467；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响；效果2：T1 975; T2 1,365; T3 1,950（召唤物伤害系数×0.65）（每跳）</t>
         </is>
       </c>
     </row>
@@ -8893,7 +8893,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,476-13,969；T2 13,266-19,557；T3 18,952-27,938（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：T1 2,500; T2 3,500; T3 5,000（每跳）</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,113-13,396；T2 12,758-18,754；T3 18,225-26,792（基础区间×武器调谐倍率1.35×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约215-289；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 8,169-12,042；T2 11,436-16,859；T3 16,338-24,085（基础区间×武器调谐倍率1.25×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：T1 1,500; T2 2,100; T3 3,000（每跳）</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,442-13,005；T2 13,218-18,207；T3 18,883-26,010（基础区间×武器调谐倍率1.15×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 9,443-13,006；T2 13,220-18,209；T3 18,886-26,013（基础区间×武器调谐倍率1.15×Boss模板×Tier）</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：远程武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 1,784-2,622；T2 2,497-3,670；T3 3,568-5,243（基础区间×武器调谐倍率1.2×damageCoefficient×0.65×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约107-143；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,905-16,398；T2 16,666-22,957；T3 23,809-32,796（基础区间×武器调谐倍率1.45×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：T1 1,500; T2 2,100; T3 3,000（每跳）</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 2,064-2,840；T2 2,890-3,976；T3 4,129-5,681（基础区间×武器调谐倍率1.15×damageCoefficient×0.65×Tier）；效果2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 1,232-1,697；T2 1,725-2,376；T3 2,464-3,395（基础区间×武器调谐倍率1.15×damageCoefficient×0.65×Tier）</t>
+          <t xml:space="preserve">效果1+2：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 1,239-1,704；T2 1,734-2,386；T3 2,477-3,408（基础区间×武器调谐倍率1.15×damageCoefficient×0.65×Tier）</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t xml:space="preserve">效果1：主手武器伤害估算区间（不含增减益/目标减伤/暴击）：T1 11,188-15,406；T2 15,663-21,568；T3 22,375-30,812（基础区间×武器调谐倍率1.35×Boss模板×Tier）</t>
+          <t xml:space="preserve">效果1：DBC基础约77-103；当前脚本未写入固定基线，实际值受法术等级/生物等级缩放影响</t>
         </is>
       </c>
     </row>
